--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_66_R7.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_66_R7.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>S. HERRERA</t>
+          <t>Y. OUATTARA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.8427</v>
+        <v>2.2471</v>
       </c>
       <c r="E2" t="n">
-        <v>2.8281</v>
+        <v>2.0728</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0146</v>
+        <v>0.1743</v>
       </c>
       <c r="G2" t="n">
-        <v>0.541</v>
+        <v>1.1954</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.6264999999999999</v>
+        <v>-1.7791</v>
       </c>
       <c r="I2" t="n">
-        <v>1.1676</v>
+        <v>2.9745</v>
       </c>
       <c r="J2" t="n">
-        <v>1.4525</v>
+        <v>1.9389</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1211</v>
+        <v>-1.1995</v>
       </c>
       <c r="L2" t="n">
-        <v>1.3314</v>
+        <v>3.1383</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.9115</v>
+        <v>-0.7433999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.7477</v>
+        <v>-0.5796</v>
       </c>
       <c r="O2" t="n">
         <v>-0.1638</v>
       </c>
       <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
         <v>-1.1598</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>-2.3195</v>
       </c>
       <c r="R2" t="n">
         <v>1.1598</v>
       </c>
       <c r="S2" t="n">
-        <v>2.2475</v>
+        <v>1.0517</v>
       </c>
       <c r="T2" t="n">
-        <v>2.4812</v>
+        <v>1.2937</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2337</v>
+        <v>-0.242</v>
       </c>
       <c r="V2" t="n">
-        <v>1.214</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1.214</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. HOMMES</t>
+          <t>S. HERRERA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.4298</v>
+        <v>2.0814</v>
       </c>
       <c r="E3" t="n">
-        <v>1.8861</v>
+        <v>1.798</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.4563</v>
+        <v>0.2834</v>
       </c>
       <c r="G3" t="n">
-        <v>3.9506</v>
+        <v>0.541</v>
       </c>
       <c r="H3" t="n">
-        <v>0.598</v>
+        <v>-0.6264999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>3.3526</v>
+        <v>1.1676</v>
       </c>
       <c r="J3" t="n">
-        <v>3.4933</v>
+        <v>1.4525</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0336</v>
+        <v>0.1211</v>
       </c>
       <c r="L3" t="n">
-        <v>3.4597</v>
+        <v>1.3314</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4574</v>
+        <v>-0.9115</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5644</v>
+        <v>-0.7477</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.107</v>
+        <v>-0.1638</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R3" t="n">
         <v>1.1598</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.0543</v>
+        <v>1.4861</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.731</v>
+        <v>1.451</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3233</v>
+        <v>0.0351</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.4665</v>
+        <v>1.214</v>
       </c>
       <c r="W3" t="n">
-        <v>0.2836</v>
+        <v>1.214</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.7501</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Y. OUATTARA</t>
+          <t>D. HOMMES</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,40 +721,40 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3975</v>
+        <v>1.8001</v>
       </c>
       <c r="E4" t="n">
-        <v>1.2904</v>
+        <v>2.122</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1071</v>
+        <v>-0.3219</v>
       </c>
       <c r="G4" t="n">
-        <v>1.1954</v>
+        <v>3.9506</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.7791</v>
+        <v>0.598</v>
       </c>
       <c r="I4" t="n">
-        <v>2.9745</v>
+        <v>3.3526</v>
       </c>
       <c r="J4" t="n">
-        <v>1.9389</v>
+        <v>3.4933</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.1995</v>
+        <v>0.0336</v>
       </c>
       <c r="L4" t="n">
-        <v>3.1383</v>
+        <v>3.4597</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.7433999999999999</v>
+        <v>0.4574</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5796</v>
+        <v>0.5644</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.1638</v>
+        <v>-0.107</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -766,28 +766,28 @@
         <v>1.1598</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2021</v>
+        <v>-0.6840000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5113</v>
+        <v>-0.4951</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3093</v>
+        <v>-0.1889</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-1.4665</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.2836</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.7501</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L. CAVALIERE</t>
+          <t>D. WILLIS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0652</v>
+        <v>0.5316</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0487</v>
+        <v>1.1574</v>
       </c>
       <c r="F5" t="n">
-        <v>1.0166</v>
+        <v>-0.6257</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.6587</v>
+        <v>0.4992</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.0971</v>
+        <v>0.1646</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4384</v>
+        <v>0.3346</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.4655</v>
+        <v>1.2318</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.5391</v>
+        <v>0.8907</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0736</v>
+        <v>0.3412</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1933</v>
+        <v>-0.7326</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5581</v>
+        <v>-0.7261</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3648</v>
+        <v>-0.0065</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6959</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R5" t="n">
-        <v>0.6959</v>
+        <v>1.1598</v>
       </c>
       <c r="S5" t="n">
-        <v>1.8864</v>
+        <v>1.1046</v>
       </c>
       <c r="T5" t="n">
-        <v>1.3724</v>
+        <v>1.0853</v>
       </c>
       <c r="U5" t="n">
-        <v>0.514</v>
+        <v>0.0193</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1418</v>
+        <v>-1.0722</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. WILLIS</t>
+          <t>L. CAVALIERE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4646</v>
+        <v>0.3485</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4182</v>
+        <v>-0.4664</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0464</v>
+        <v>0.8149</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4992</v>
+        <v>-1.6587</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1646</v>
+        <v>-2.0971</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3346</v>
+        <v>0.4384</v>
       </c>
       <c r="J6" t="n">
-        <v>1.2318</v>
+        <v>-1.4655</v>
       </c>
       <c r="K6" t="n">
-        <v>0.8907</v>
+        <v>-1.5391</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3412</v>
+        <v>0.0736</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.7326</v>
+        <v>-0.1933</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.7261</v>
+        <v>-0.5581</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0065</v>
+        <v>0.3648</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>0.6959</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1598</v>
+        <v>0.6959</v>
       </c>
       <c r="S6" t="n">
-        <v>1.0376</v>
+        <v>1.1696</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3462</v>
+        <v>0.8573</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6915</v>
+        <v>0.3123</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.0722</v>
+        <v>0.1418</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. FAYE</t>
+          <t>J. ROBINSON</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0431</v>
+        <v>0.2815</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6637999999999999</v>
+        <v>0.4917</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.7069</v>
+        <v>-0.2102</v>
       </c>
       <c r="G7" t="n">
-        <v>1.4683</v>
+        <v>-0.133</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.1211</v>
+        <v>0.9446</v>
       </c>
       <c r="I7" t="n">
-        <v>1.5894</v>
+        <v>-1.0775</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5179</v>
+        <v>0.925</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.1814</v>
+        <v>1.8387</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6993</v>
+        <v>-0.9137</v>
       </c>
       <c r="M7" t="n">
-        <v>0.9503</v>
+        <v>-1.058</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0602</v>
+        <v>-0.8942</v>
       </c>
       <c r="O7" t="n">
-        <v>0.8901</v>
+        <v>-0.1638</v>
       </c>
       <c r="P7" t="n">
-        <v>1.1598</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R7" t="n">
         <v>1.1598</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1511</v>
+        <v>0.6438</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1458</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0053</v>
+        <v>-0.1702</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.8223</v>
+        <v>0.9304</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.8223</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. ROBINSON</t>
+          <t>M. FAYE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.417</v>
+        <v>-0.0939</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.8372000000000001</v>
+        <v>0.5458</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5799</v>
+        <v>-0.6397</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.133</v>
+        <v>1.4683</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9446</v>
+        <v>-0.1211</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.0775</v>
+        <v>1.5894</v>
       </c>
       <c r="J8" t="n">
-        <v>0.925</v>
+        <v>0.5179</v>
       </c>
       <c r="K8" t="n">
-        <v>1.8387</v>
+        <v>-0.1814</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.9137</v>
+        <v>0.6993</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.058</v>
+        <v>0.9503</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.8942</v>
+        <v>0.0602</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.1638</v>
+        <v>0.8901</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.1598</v>
+        <v>1.1598</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>1.1598</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.0548</v>
+        <v>0.1004</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5149</v>
+        <v>0.0279</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5399</v>
+        <v>0.0725</v>
       </c>
       <c r="V8" t="n">
-        <v>0.9304</v>
+        <v>-2.8223</v>
       </c>
       <c r="W8" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1418</v>
+        <v>-2.8223</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. DOKOSSI</t>
+          <t>N. HIFI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.5678</v>
+        <v>-1.4635</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4205</v>
+        <v>-3.2163</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.9883</v>
+        <v>1.7527</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.7085</v>
+        <v>-7.6015</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1164</v>
+        <v>-3.3518</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.5921</v>
+        <v>-4.2497</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2312</v>
+        <v>-7.8153</v>
       </c>
       <c r="K9" t="n">
-        <v>0.08400000000000001</v>
+        <v>-2.8863</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1472</v>
+        <v>-4.929</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.9398</v>
+        <v>0.2139</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2004</v>
+        <v>-0.4655</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.7393999999999999</v>
+        <v>0.6793</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.6237</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q9" t="n">
         <v>-2.3195</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6959</v>
+        <v>1.3917</v>
       </c>
       <c r="S9" t="n">
-        <v>2.3727</v>
+        <v>0.0964</v>
       </c>
       <c r="T9" t="n">
-        <v>2.3669</v>
+        <v>-0.0507</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0057</v>
+        <v>0.1472</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.6083</v>
+        <v>6.9693</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1418</v>
+        <v>6.9693</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.7501</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>N. HIFI</t>
+          <t>A. DOKOSSI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.464</v>
+        <v>-2.8407</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.8807</v>
+        <v>-0.6844</v>
       </c>
       <c r="F10" t="n">
-        <v>1.4167</v>
+        <v>-2.1563</v>
       </c>
       <c r="G10" t="n">
-        <v>-7.6015</v>
+        <v>-0.7085</v>
       </c>
       <c r="H10" t="n">
-        <v>-3.3518</v>
+        <v>-0.1164</v>
       </c>
       <c r="I10" t="n">
-        <v>-4.2497</v>
+        <v>-0.5921</v>
       </c>
       <c r="J10" t="n">
-        <v>-7.8153</v>
+        <v>0.2312</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.8863</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>-4.929</v>
+        <v>0.1472</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2139</v>
+        <v>-0.9398</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.4655</v>
+        <v>-0.2004</v>
       </c>
       <c r="O10" t="n">
-        <v>0.6793</v>
+        <v>-0.7393999999999999</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.9278</v>
+        <v>-1.6237</v>
       </c>
       <c r="Q10" t="n">
         <v>-2.3195</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3917</v>
+        <v>0.6959</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9041</v>
+        <v>1.0998</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7151999999999999</v>
+        <v>1.2621</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1889</v>
+        <v>-0.1623</v>
       </c>
       <c r="V10" t="n">
-        <v>6.9693</v>
+        <v>-1.6083</v>
       </c>
       <c r="W10" t="n">
-        <v>6.9693</v>
+        <v>0.1418</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.7501</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.5425</v>
+        <v>-2.9636</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.7583</v>
+        <v>-2.1121</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.7842</v>
+        <v>-0.8515</v>
       </c>
       <c r="G11" t="n">
         <v>-0.1911</v>
@@ -1312,13 +1312,13 @@
         <v>0.6959</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3444</v>
+        <v>-0.0767</v>
       </c>
       <c r="T11" t="n">
-        <v>0.4876</v>
+        <v>0.1338</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1432</v>
+        <v>-0.2104</v>
       </c>
       <c r="V11" t="n">
         <v>-1.0722</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.5281</v>
+        <v>-3.225</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.6945</v>
+        <v>-1.4586</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.8336</v>
+        <v>-1.7664</v>
       </c>
       <c r="G12" t="n">
         <v>0.2669</v>
@@ -1390,13 +1390,13 @@
         <v>0.9278</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.3311</v>
+        <v>-1.028</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5895</v>
+        <v>-0.3536</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.7415</v>
+        <v>-0.6743</v>
       </c>
       <c r="V12" t="n">
         <v>-1.0722</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.275</v>
+        <v>-5.5946</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.7472</v>
+        <v>-5.8651</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4722</v>
+        <v>0.2705</v>
       </c>
       <c r="G13" t="n">
         <v>-2.602</v>
@@ -1468,13 +1468,13 @@
         <v>1.3917</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4867</v>
+        <v>0.1672</v>
       </c>
       <c r="T13" t="n">
-        <v>0.4446</v>
+        <v>0.3266</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0422</v>
+        <v>-0.1595</v>
       </c>
       <c r="V13" t="n">
         <v>-1.0722</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-9.637700000000001</v>
+        <v>-8.891100000000002</v>
       </c>
       <c r="E14" t="n">
-        <v>-6.3621</v>
+        <v>-5.6152</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.2756</v>
+        <v>-3.2759</v>
       </c>
       <c r="G14" t="n">
         <v>-4.9734</v>
@@ -1519,25 +1519,25 @@
         <v>5.002</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.9145000000000008</v>
+        <v>-0.9144999999999992</v>
       </c>
       <c r="K14" t="n">
         <v>-4.9116</v>
       </c>
       <c r="L14" t="n">
-        <v>3.997100000000001</v>
+        <v>3.9971</v>
       </c>
       <c r="M14" t="n">
         <v>-4.0589</v>
       </c>
       <c r="N14" t="n">
-        <v>-5.063899999999999</v>
+        <v>-5.0639</v>
       </c>
       <c r="O14" t="n">
         <v>1.005</v>
       </c>
       <c r="P14" t="n">
-        <v>-8.118400000000001</v>
+        <v>-8.118399999999999</v>
       </c>
       <c r="Q14" t="n">
         <v>-20.8757</v>
@@ -1546,16 +1546,16 @@
         <v>12.7577</v>
       </c>
       <c r="S14" t="n">
-        <v>4.384200000000001</v>
+        <v>5.130900000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>5.605399999999999</v>
+        <v>6.3523</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.2211</v>
+        <v>-1.2212</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.9304000000000001</v>
+        <v>-0.9303999999999992</v>
       </c>
       <c r="W14" t="n">
         <v>9.822699999999999</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>8.4232</v>
+        <v>8.1366</v>
       </c>
       <c r="E15" t="n">
-        <v>4.5923</v>
+        <v>3.7666</v>
       </c>
       <c r="F15" t="n">
-        <v>3.831</v>
+        <v>4.37</v>
       </c>
       <c r="G15" t="n">
         <v>4.1415</v>
@@ -1624,13 +1624,13 @@
         <v>3.7112</v>
       </c>
       <c r="S15" t="n">
-        <v>0.6581</v>
+        <v>0.3714</v>
       </c>
       <c r="T15" t="n">
-        <v>1.86</v>
+        <v>1.0343</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.2019</v>
+        <v>-0.6629</v>
       </c>
       <c r="V15" t="n">
         <v>1.0722</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.6358</v>
+        <v>5.23</v>
       </c>
       <c r="E16" t="n">
-        <v>1.8519</v>
+        <v>2.3237</v>
       </c>
       <c r="F16" t="n">
-        <v>1.7839</v>
+        <v>2.9063</v>
       </c>
       <c r="G16" t="n">
         <v>2.7391</v>
@@ -1702,13 +1702,13 @@
         <v>3.2473</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.6395</v>
+        <v>-0.0452</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0861</v>
+        <v>0.3857</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.5534</v>
+        <v>-0.4309</v>
       </c>
       <c r="V16" t="n">
         <v>1.6083</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.4474</v>
+        <v>3.4195</v>
       </c>
       <c r="E17" t="n">
-        <v>1.5889</v>
+        <v>1.471</v>
       </c>
       <c r="F17" t="n">
-        <v>1.8585</v>
+        <v>1.9485</v>
       </c>
       <c r="G17" t="n">
         <v>1.2708</v>
@@ -1780,13 +1780,13 @@
         <v>1.1598</v>
       </c>
       <c r="S17" t="n">
-        <v>0.8751</v>
+        <v>0.8472</v>
       </c>
       <c r="T17" t="n">
-        <v>0.8022</v>
+        <v>0.6842</v>
       </c>
       <c r="U17" t="n">
-        <v>0.07290000000000001</v>
+        <v>0.163</v>
       </c>
       <c r="V17" t="n">
         <v>0.1418</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.3989</v>
+        <v>3.3939</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.3156</v>
+        <v>0.5101</v>
       </c>
       <c r="F18" t="n">
-        <v>2.7145</v>
+        <v>2.8838</v>
       </c>
       <c r="G18" t="n">
         <v>1.7276</v>
@@ -1858,13 +1858,13 @@
         <v>2.0876</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.7050999999999999</v>
+        <v>0.2899</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7389</v>
+        <v>0.0868</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0338</v>
+        <v>0.2032</v>
       </c>
       <c r="V18" t="n">
         <v>1.6083</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.648</v>
+        <v>2.8047</v>
       </c>
       <c r="E19" t="n">
-        <v>0.551</v>
+        <v>0.7869</v>
       </c>
       <c r="F19" t="n">
-        <v>1.0969</v>
+        <v>2.0177</v>
       </c>
       <c r="G19" t="n">
         <v>0.5874</v>
@@ -1936,13 +1936,13 @@
         <v>3.0154</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.1018</v>
+        <v>0.0549</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2873</v>
+        <v>0.5232</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.3891</v>
+        <v>-0.4683</v>
       </c>
       <c r="V19" t="n">
         <v>1.4665</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.04</v>
+        <v>-0.0394</v>
       </c>
       <c r="E20" t="n">
-        <v>3.3513</v>
+        <v>3.1154</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.3913</v>
+        <v>-3.1548</v>
       </c>
       <c r="G20" t="n">
         <v>0.9733000000000001</v>
@@ -2014,13 +2014,13 @@
         <v>1.8556</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1885</v>
+        <v>-0.1878</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1845</v>
+        <v>-0.4204</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0039</v>
+        <v>0.2326</v>
       </c>
       <c r="V20" t="n">
         <v>-2.6805</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.9068000000000001</v>
+        <v>-0.6995</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.7949</v>
+        <v>-1.9129</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8881</v>
+        <v>1.2134</v>
       </c>
       <c r="G22" t="n">
         <v>-0.8978</v>
@@ -2170,13 +2170,13 @@
         <v>2.5515</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1867</v>
+        <v>0.0206</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0193</v>
+        <v>-0.1373</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1674</v>
+        <v>0.1579</v>
       </c>
       <c r="V22" t="n">
         <v>-1.214</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.0397</v>
+        <v>-0.8152</v>
       </c>
       <c r="E23" t="n">
         <v>-0.8144</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.2253</v>
+        <v>-0.0008</v>
       </c>
       <c r="G23" t="n">
         <v>-0.9144</v>
@@ -2248,13 +2248,13 @@
         <v>1.1598</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.1975</v>
+        <v>-0.973</v>
       </c>
       <c r="T23" t="n">
         <v>-0.3734</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.8241000000000001</v>
+        <v>-0.5996</v>
       </c>
       <c r="V23" t="n">
         <v>1.0722</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.561</v>
+        <v>-7.4931</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.1987</v>
+        <v>-5.4346</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.3623</v>
+        <v>-2.0585</v>
       </c>
       <c r="G24" t="n">
         <v>-4.2863</v>
@@ -2326,13 +2326,13 @@
         <v>2.0876</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.8984</v>
+        <v>-0.8305</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.326</v>
+        <v>-0.5619</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.5724</v>
+        <v>-0.2686</v>
       </c>
       <c r="V24" t="n">
         <v>-2.1444</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>9.637799999999999</v>
+        <v>13.5695</v>
       </c>
       <c r="E25" t="n">
-        <v>3.811800000000001</v>
+        <v>3.811800000000002</v>
       </c>
       <c r="F25" t="n">
-        <v>5.826000000000001</v>
+        <v>9.757599999999998</v>
       </c>
       <c r="G25" t="n">
         <v>4.973199999999999</v>
@@ -2404,13 +2404,13 @@
         <v>20.8758</v>
       </c>
       <c r="S25" t="n">
-        <v>-4.3843</v>
+        <v>-0.4525</v>
       </c>
       <c r="T25" t="n">
-        <v>1.2213</v>
+        <v>1.2212</v>
       </c>
       <c r="U25" t="n">
-        <v>-5.605499999999999</v>
+        <v>-1.6736</v>
       </c>
       <c r="V25" t="n">
         <v>0.9304000000000001</v>
